--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jul-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -18373,7 +18373,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18495,7 +18495,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19593,7 +19593,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jul-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M349"/>
+  <dimension ref="A1:M350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1448,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1513,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1578,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1704,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1769,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1834,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1899,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1964,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2029,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2094,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2281,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2346,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2411,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2537,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2602,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2667,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2732,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2797,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2862,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2927,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2992,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3118,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3183,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3248,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3374,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3500,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3565,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3630,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3695,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3760,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3825,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3951,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4077,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4142,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4207,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4272,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4337,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4402,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4467,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4532,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4597,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4662,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4788,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5036,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5101,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5166,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5231,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5296,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5361,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5487,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5552,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5678,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5743,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5808,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5873,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5938,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6003,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6068,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6194,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6259,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6324,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6389,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6454,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6519,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6584,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6710,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6775,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6840,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6905,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6970,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7035,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7100,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7230,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7295,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7360,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7486,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7551,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7738,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7803,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +7990,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8055,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8120,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8246,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8311,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8441,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8506,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8632,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8317,7 +8697,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8378,7 +8762,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8827,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8565,7 +8957,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8626,7 +9022,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8687,7 +9087,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8748,7 +9152,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8809,7 +9217,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8870,7 +9282,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9053,7 +9469,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9114,7 +9534,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9175,7 +9599,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9297,7 +9725,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9358,7 +9790,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9480,7 +9916,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9602,7 +10042,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9663,7 +10107,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9724,7 +10172,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9785,7 +10237,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9846,7 +10302,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9907,7 +10367,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9968,7 +10432,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10029,7 +10497,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10090,7 +10562,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10151,7 +10627,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10395,7 +10875,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10456,7 +10940,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10517,7 +11005,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10578,7 +11070,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10639,7 +11135,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10761,7 +11261,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10822,7 +11326,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10883,7 +11391,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11005,7 +11517,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11066,7 +11582,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11188,7 +11708,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11249,7 +11773,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11310,7 +11838,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11371,7 +11903,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11432,7 +11968,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11445,7 +11985,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>564162-642-CM26</t>
+          <t>564162-643-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11465,7 +12005,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -11485,22 +12025,26 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>5592.98</v>
+        <v>521.15</v>
       </c>
     </row>
     <row r="182">
@@ -11750,7 +12294,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>564162-643-CM26</t>
+          <t>1432083-1658-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11775,43 +12319,47 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>521.15</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1432083-1658-CM26</t>
+          <t>564162-642-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11831,32 +12379,32 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11866,7 +12414,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1134</v>
+        <v>5592.98</v>
       </c>
     </row>
     <row r="188">
@@ -11920,7 +12468,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12042,7 +12594,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12103,7 +12659,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12164,7 +12724,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12225,7 +12789,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12286,7 +12854,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12347,7 +12919,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12408,7 +12984,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12469,7 +13049,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12530,7 +13114,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12591,7 +13179,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12652,7 +13244,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12713,7 +13309,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12774,7 +13374,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12896,7 +13500,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12957,7 +13565,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13018,7 +13630,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13079,7 +13695,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13140,7 +13760,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13201,7 +13825,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13323,7 +13951,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13384,7 +14016,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13445,7 +14081,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13506,7 +14146,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13567,7 +14211,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13628,7 +14276,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13689,7 +14341,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13994,7 +14650,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14055,7 +14715,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14116,7 +14780,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14177,7 +14845,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14238,7 +14910,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14299,7 +14975,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14360,7 +15040,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14421,7 +15105,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14482,7 +15170,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14543,7 +15235,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14665,7 +15361,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14726,7 +15426,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14787,7 +15491,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14848,7 +15556,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14970,7 +15682,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15092,7 +15808,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15214,7 +15934,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15336,7 +16060,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15458,7 +16186,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15519,7 +16251,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15580,7 +16316,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15641,7 +16381,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15763,7 +16507,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15885,7 +16633,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15946,7 +16698,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15959,7 +16715,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>603663-141-CM26</t>
+          <t>2328-906-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15984,37 +16740,41 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>863.1799999999999</v>
+        <v>10714.57</v>
       </c>
     </row>
     <row r="256">
@@ -16129,7 +16889,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16190,7 +16954,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16264,7 +17032,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2328-906-CM26</t>
+          <t>603663-141-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16289,27 +17057,27 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16319,7 +17087,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>10714.57</v>
+        <v>863.1799999999999</v>
       </c>
     </row>
     <row r="261">
@@ -16556,7 +17324,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16617,7 +17389,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16678,7 +17454,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16739,7 +17519,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16800,7 +17584,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16861,7 +17649,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16922,7 +17714,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16983,7 +17779,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17105,7 +17905,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17166,7 +17970,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17410,7 +18218,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17471,7 +18283,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17532,7 +18348,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17593,7 +18413,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17715,7 +18539,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17776,7 +18604,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17837,7 +18669,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17959,7 +18795,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18020,7 +18860,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18081,7 +18925,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18142,7 +18990,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18386,7 +19238,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18447,7 +19303,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18569,7 +19429,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18630,7 +19494,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18691,7 +19559,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18752,7 +19624,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18813,7 +19689,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18874,7 +19754,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18935,7 +19819,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18996,7 +19884,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19057,7 +19949,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19192,7 +20088,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1110404-708-CM26</t>
+          <t>3810-609-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19217,27 +20113,27 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19247,13 +20143,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1012.64</v>
+        <v>1589.82</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>3810-609-CM26</t>
+          <t>1110404-708-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19278,37 +20174,41 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K309" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1589.82</v>
+        <v>1012.64</v>
       </c>
     </row>
     <row r="310">
@@ -19362,7 +20262,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19423,7 +20327,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19484,7 +20392,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19545,7 +20457,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19606,7 +20522,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19667,7 +20587,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19728,7 +20652,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19789,7 +20717,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19863,7 +20795,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5531-165-CM26</t>
+          <t>1298355-621-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -19888,12 +20820,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -19903,28 +20835,32 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K319" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1239.48</v>
+        <v>1141.57</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1298355-621-CM26</t>
+          <t>564162-704-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -19944,17 +20880,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -19964,28 +20900,32 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>1141.57</v>
+        <v>1956.12</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>564162-704-CM26</t>
+          <t>3047-376-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20005,48 +20945,52 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K321" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1956.12</v>
+        <v>10245.94</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3047-376-CM26</t>
+          <t>2328-961-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20066,48 +21010,52 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K322" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>10245.94</v>
+        <v>9592.59</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2328-961-CM26</t>
+          <t>3035-321-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20127,32 +21075,32 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K323" t="inlineStr"/>
@@ -20162,13 +21110,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>9592.59</v>
+        <v>2258.62</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>3035-321-CM26</t>
+          <t>2328-958-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20188,42 +21136,46 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2258.62</v>
+        <v>11859.09</v>
       </c>
     </row>
     <row r="325">
@@ -20277,7 +21229,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20290,7 +21246,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2328-958-CM26</t>
+          <t>5531-165-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20310,48 +21266,52 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K326" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>11859.09</v>
+        <v>1239.48</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1110404-709-CM26</t>
+          <t>85-213-CC26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20371,48 +21331,52 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>6369.95</v>
+        <v>9204.889999999999</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1460278-310-CM26</t>
+          <t>1110404-709-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20432,22 +21396,22 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20460,20 +21424,24 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>9554.93</v>
+        <v>6369.95</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2294-1411-CM26</t>
+          <t>1460278-310-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -20498,43 +21466,47 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>3956.75</v>
+        <v>9554.93</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>757818-219-CM26</t>
+          <t>2294-1411-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -20559,43 +21531,47 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>69.091.000-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PALMILLA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K330" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>4183.97</v>
+        <v>3956.75</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2294-1127-CM26</t>
+          <t>757818-219-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -20620,43 +21596,47 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.091.000-4</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PALMILLA</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K331" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2384.72</v>
+        <v>4183.97</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1233613-1287-CM26</t>
+          <t>2294-1127-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -20676,32 +21656,32 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -20711,13 +21691,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1070.98</v>
+        <v>2384.72</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>5864-40-CM26</t>
+          <t>1233613-1287-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -20737,48 +21717,52 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>2713.91</v>
+        <v>1070.98</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1110404-737-CM26</t>
+          <t>5864-40-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -20793,22 +21777,22 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -20818,28 +21802,32 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>612.47</v>
+        <v>2713.91</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>4179-889-CM26</t>
+          <t>1110404-737-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -20864,43 +21852,47 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>736.37</v>
+        <v>612.47</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>4179-888-CM26</t>
+          <t>4179-889-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -20948,20 +21940,24 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1910.99</v>
+        <v>736.37</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1298355-627-CM26</t>
+          <t>4179-888-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -20986,43 +21982,47 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>7143.05</v>
+        <v>1910.99</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2701-503-CM26</t>
+          <t>1298355-627-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21047,12 +22047,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21062,28 +22062,32 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>3472.72</v>
+        <v>7143.05</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2343-379-CM26</t>
+          <t>2701-503-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21103,17 +22107,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21123,12 +22127,12 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K339" t="inlineStr"/>
@@ -21138,13 +22142,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1445.49</v>
+        <v>3472.72</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1252675-45-CM26</t>
+          <t>2343-379-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21164,48 +22168,52 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>15083.61</v>
+        <v>1445.49</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3494-235-CM26</t>
+          <t>1252675-45-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21230,43 +22238,47 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>6538.24</v>
+        <v>15083.61</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1087105-17-CM26</t>
+          <t>2407-493-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21291,43 +22303,47 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>6033.44</v>
+        <v>2417.33</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2407-493-CM26</t>
+          <t>1087105-17-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21352,43 +22368,47 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2417.33</v>
+        <v>6033.44</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1261592-925-CM26</t>
+          <t>3494-235-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21408,48 +22428,52 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>22355.1</v>
+        <v>6538.24</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>3714-200-CM26</t>
+          <t>1261592-925-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -21474,27 +22498,27 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K345" t="inlineStr"/>
@@ -21504,13 +22528,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>15946</v>
+        <v>22355.1</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2428-793-CM26</t>
+          <t>3714-200-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -21535,43 +22559,47 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>1055.16</v>
+        <v>15946</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1080157-118-CM26</t>
+          <t>2428-793-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -21596,12 +22624,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21611,28 +22639,32 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>16063.57</v>
+        <v>1055.16</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5178-3359-CM26</t>
+          <t>1080157-118-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -21652,102 +22684,175 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>4128.57</v>
+        <v>16063.57</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
+          <t>5178-3359-CM26</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="n">
+        <v>4128.57</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
           <t>640840-125-CM26</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr">
+      <c r="E350" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr">
+      <c r="F350" t="inlineStr">
         <is>
           <t>69.060.700-k</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr">
+      <c r="G350" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr">
+      <c r="H350" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I349" t="inlineStr">
+      <c r="I350" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
-      <c r="J349" t="inlineStr">
+      <c r="J350" t="inlineStr">
         <is>
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M349" s="2" t="n">
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="n">
         <v>1281.42</v>
       </c>
     </row>

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jul-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jul-2026.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -12314,7 +12314,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -17426,7 +17426,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -17621,7 +17621,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -18129,7 +18129,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -18190,7 +18190,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -18255,7 +18255,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -20047,7 +20047,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -21201,7 +21201,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -21526,7 +21526,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -22168,7 +22168,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -22493,7 +22493,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -22619,7 +22619,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -22684,7 +22684,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
